--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:35</t>
+    <t xml:space="preserve">2026-09-24 01:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -806,10 +806,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.4</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -823,7 +823,7 @@
         <v>-0.09</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -834,10 +834,10 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.31</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_arica_y_parinacota.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:25</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
